--- a/todoapp test case.xlsx
+++ b/todoapp test case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\learning\todoapp_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AE75AE-76E8-40E7-AEF1-84939A54165E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572E52A4-0AAE-4054-A4FE-B2B251073640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="129">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -850,6 +850,9 @@
       <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -870,6 +873,9 @@
       <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -890,6 +896,9 @@
       <c r="F5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G5" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -910,6 +919,9 @@
       <c r="F6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G6" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -930,6 +942,9 @@
       <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G7" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -950,6 +965,9 @@
       <c r="F8" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G8" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -970,6 +988,9 @@
       <c r="F9" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G9" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -990,6 +1011,9 @@
       <c r="F10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G10" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1010,6 +1034,9 @@
       <c r="F11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G11" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1030,6 +1057,9 @@
       <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G12" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1050,6 +1080,9 @@
       <c r="F13" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G13" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1070,6 +1103,9 @@
       <c r="F14" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G14" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1090,6 +1126,9 @@
       <c r="F15" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G15" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1110,8 +1149,11 @@
       <c r="F16" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G16" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1130,8 +1172,11 @@
       <c r="F17" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G17" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -1150,8 +1195,11 @@
       <c r="F18" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1170,8 +1218,11 @@
       <c r="F19" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -1190,8 +1241,11 @@
       <c r="F20" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1210,8 +1264,11 @@
       <c r="F21" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G21" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1230,8 +1287,11 @@
       <c r="F22" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G22" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1250,8 +1310,11 @@
       <c r="F23" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G23" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>83</v>
       </c>
@@ -1270,8 +1333,11 @@
       <c r="F24" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G24" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>84</v>
       </c>
@@ -1290,8 +1356,11 @@
       <c r="F25" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G25" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>85</v>
       </c>
@@ -1310,8 +1379,11 @@
       <c r="F26" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G26" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>86</v>
       </c>
@@ -1330,8 +1402,11 @@
       <c r="F27" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G27" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -1350,8 +1425,11 @@
       <c r="F28" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G28" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>88</v>
       </c>
@@ -1370,8 +1448,11 @@
       <c r="F29" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G29" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>113</v>
       </c>
@@ -1390,8 +1471,11 @@
       <c r="F30" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G30" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>114</v>
       </c>
@@ -1410,8 +1494,11 @@
       <c r="F31" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
